--- a/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
+++ b/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T13:01:25+00:00</t>
+    <t>2026-09-16T13:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
+++ b/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T13:58:22+00:00</t>
+    <t>2026-09-16T14:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
+++ b/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:17:29+00:00</t>
+    <t>2026-09-16T14:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
+++ b/add_swagger_api_fhir/ig/StructureDefinition-as-ext-organization-closing-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:43:48+00:00</t>
+    <t>2026-09-21T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
